--- a/data/trans_orig/P05B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05B_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257730</t>
+          <t>258634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270649</t>
+          <t>270591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251238</t>
+          <t>252386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259821</t>
+          <t>259822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515759</t>
+          <t>514113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529363</t>
+          <t>529203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38984</t>
+          <t>38823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59494</t>
+          <t>61436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465132</t>
+          <t>463599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482607</t>
+          <t>482046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464965</t>
+          <t>465126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485131</t>
+          <t>484872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937530</t>
+          <t>935588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>964566</t>
+          <t>963078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>19428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46442</t>
+          <t>44889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297433</t>
+          <t>298519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311805</t>
+          <t>311359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303886</t>
+          <t>302903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321543</t>
+          <t>321648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>606917</t>
+          <t>608470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629443</t>
+          <t>629810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341280</t>
+          <t>340757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353984</t>
+          <t>353863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353914</t>
+          <t>353813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365865</t>
+          <t>366089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>699616</t>
+          <t>699674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718562</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29219</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>47894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179450</t>
+          <t>179266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194339</t>
+          <t>194261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176825</t>
+          <t>176786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193344</t>
+          <t>192979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362278</t>
+          <t>361458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384196</t>
+          <t>384067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262129</t>
+          <t>262773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269932</t>
+          <t>269939</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266540</t>
+          <t>266331</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276229</t>
+          <t>276177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>533498</t>
+          <t>533109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>545037</t>
+          <t>544997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>55193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41291</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68456</t>
+          <t>69617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>593699</t>
+          <t>592985</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607320</t>
+          <t>607292</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>581801</t>
+          <t>583026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>606848</t>
+          <t>608597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1183969</t>
+          <t>1182808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1211134</t>
+          <t>1212459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>30720</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>19991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41756</t>
+          <t>40658</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34513</t>
+          <t>35778</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62865</t>
+          <t>63264</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>711066</t>
+          <t>710676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>729455</t>
+          <t>730161</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>741755</t>
+          <t>742853</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763973</t>
+          <t>763520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1462042</t>
+          <t>1461643</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1490394</t>
+          <t>1489129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>79226</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118038</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135783</t>
+          <t>135032</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>183332</t>
+          <t>183299</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>224001</t>
+          <t>225037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>289091</t>
+          <t>289010</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3154386</t>
+          <t>3153265</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3194603</t>
+          <t>3193198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3194241</t>
+          <t>3194274</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3241790</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6360906</t>
+          <t>6360987</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6425996</t>
+          <t>6424960</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275493</t>
+          <t>276060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288165</t>
+          <t>287988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264270</t>
+          <t>263565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275783</t>
+          <t>276163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545988</t>
+          <t>545275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561980</t>
+          <t>562580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37212</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33121</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63031</t>
+          <t>60961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468315</t>
+          <t>467860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490100</t>
+          <t>489487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490324</t>
+          <t>489730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508763</t>
+          <t>509073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>964118</t>
+          <t>966188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>994028</t>
+          <t>993315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>336050</t>
+          <t>336121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659180</t>
+          <t>660119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15443</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361755</t>
+          <t>362961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371964</t>
+          <t>371989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372552</t>
+          <t>372815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384005</t>
+          <t>384839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739798</t>
+          <t>740289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754560</t>
+          <t>754602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201481</t>
+          <t>201745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210765</t>
+          <t>210729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204994</t>
+          <t>206605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>217599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412176</t>
+          <t>412242</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426430</t>
+          <t>426045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267070</t>
+          <t>267870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272513</t>
+          <t>272310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544464</t>
+          <t>544574</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>552023</t>
+          <t>552022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,47 +6129,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5696</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14019</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5696</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>14256</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649217</t>
+          <t>649959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658795</t>
+          <t>658742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,49 +6242,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>687134</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>678811</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>690959</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>687134</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>678574</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>691054</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1242</t>
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1333538</t>
+          <t>1333835</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348524</t>
+          <t>1348532</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>755409</t>
+          <t>754138</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768286</t>
+          <t>768173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>807229</t>
+          <t>806812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>816739</t>
+          <t>816766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1565994</t>
+          <t>1565744</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1582473</t>
+          <t>1582930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73995</t>
+          <t>72273</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42825</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>73961</t>
+          <t>74619</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93701</t>
+          <t>94193</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>137168</t>
+          <t>141390</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3338807</t>
+          <t>3340529</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3369810</t>
+          <t>3370708</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3467626</t>
+          <t>3466968</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3498762</t>
+          <t>3498440</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6817221</t>
+          <t>6812999</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6860688</t>
+          <t>6860196</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22919</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42103</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266506</t>
+          <t>267435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283688</t>
+          <t>283727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265784</t>
+          <t>265833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280327</t>
+          <t>281029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539369</t>
+          <t>538712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>560900</t>
+          <t>560877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>22261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>36440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27244</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53001</t>
+          <t>54198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480435</t>
+          <t>480314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495416</t>
+          <t>495405</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485541</t>
+          <t>486644</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506742</t>
+          <t>506429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>972658</t>
+          <t>971461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>998415</t>
+          <t>998984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308357</t>
+          <t>308835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329268</t>
+          <t>328277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641728</t>
+          <t>643746</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653110</t>
+          <t>653108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27853</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358531</t>
+          <t>358298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366277</t>
+          <t>366252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357465</t>
+          <t>358919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>373848</t>
+          <t>374314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720345</t>
+          <t>721316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>738692</t>
+          <t>738850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210150</t>
+          <t>210119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217701</t>
+          <t>217712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421602</t>
+          <t>421345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428933</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258953</t>
+          <t>258527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265915</t>
+          <t>265901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>528041</t>
+          <t>528137</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20499</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30515</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634570</t>
+          <t>635415</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647746</t>
+          <t>648514</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>665961</t>
+          <t>666514</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>680189</t>
+          <t>680218</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1307625</t>
+          <t>1306886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1326273</t>
+          <t>1325993</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>771944</t>
+          <t>771901</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812099</t>
+          <t>811867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>823825</t>
+          <t>823804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1587789</t>
+          <t>1588482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1600804</t>
+          <t>1600651</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62825</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59492</t>
+          <t>58836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97187</t>
+          <t>94563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>100422</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145077</t>
+          <t>147346</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3322810</t>
+          <t>3324342</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3352148</t>
+          <t>3352559</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3433326</t>
+          <t>3435950</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3471021</t>
+          <t>3471677</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6771071</t>
+          <t>6768802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6815926</t>
+          <t>6815726</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>716</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>716</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -10810,17 +10810,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310745</t>
+          <t>318129</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307317</t>
+          <t>315072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -10880,27 +10880,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>600379</t>
+          <t>634190</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596947</t>
+          <t>630210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,22 +11040,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,67 +11075,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>8126</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3420</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>15456</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>8089</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>15732</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -11153,27 +11153,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511323</t>
+          <t>523635</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>503848</t>
+          <t>516196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514264</t>
+          <t>526535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11188,67 +11188,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>511065</t>
+          <t>542557</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507059</t>
+          <t>538049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513571</t>
+          <t>545163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1066192</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1058862</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1070898</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>99,24%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1022388</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1014745</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1026724</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>515508</t>
+          <t>527824</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>515508</t>
+          <t>527824</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>515508</t>
+          <t>527824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030477</t>
+          <t>1074318</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030477</t>
+          <t>1074318</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030477</t>
+          <t>1074318</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15082</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>32615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>301728</t>
+          <t>300768</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292791</t>
+          <t>291304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308103</t>
+          <t>306298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>336516</t>
+          <t>344003</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328235</t>
+          <t>336398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341420</t>
+          <t>349110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>638244</t>
+          <t>644770</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626122</t>
+          <t>634767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646628</t>
+          <t>653159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314233</t>
+          <t>312645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314233</t>
+          <t>312645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314233</t>
+          <t>312645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347477</t>
+          <t>354738</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347477</t>
+          <t>354738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347477</t>
+          <t>354738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>661710</t>
+          <t>667382</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>661710</t>
+          <t>667382</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>661710</t>
+          <t>667382</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28194</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302904</t>
+          <t>363189</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293683</t>
+          <t>353654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307713</t>
+          <t>367712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>463385</t>
+          <t>409052</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>457613</t>
+          <t>403150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>468134</t>
+          <t>413026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>766290</t>
+          <t>772241</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>756689</t>
+          <t>761993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>773663</t>
+          <t>778627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311952</t>
+          <t>372451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311952</t>
+          <t>372451</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311952</t>
+          <t>372451</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>472930</t>
+          <t>418955</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>472930</t>
+          <t>418955</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>472930</t>
+          <t>418955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>784883</t>
+          <t>791406</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>784883</t>
+          <t>791406</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>784883</t>
+          <t>791406</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>716</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>339</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178095</t>
+          <t>204949</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175260</t>
+          <t>202084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>258028</t>
+          <t>228123</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256740</t>
+          <t>226766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258343</t>
+          <t>228462</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>436122</t>
+          <t>433072</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433501</t>
+          <t>429616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437085</t>
+          <t>434127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258343</t>
+          <t>228462</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258343</t>
+          <t>228462</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258343</t>
+          <t>228462</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437085</t>
+          <t>434127</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437085</t>
+          <t>434127</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437085</t>
+          <t>434127</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -12525,27 +12525,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>267429</t>
+          <t>268675</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262222</t>
+          <t>263075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>254595</t>
+          <t>261333</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>257849</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256161</t>
+          <t>262960</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>522024</t>
+          <t>530008</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>515840</t>
+          <t>524678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>524897</t>
+          <t>532694</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>619960</t>
+          <t>713461</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>614192</t>
+          <t>706288</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>622861</t>
+          <t>716627</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>833295</t>
+          <t>753772</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>823877</t>
+          <t>746238</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840774</t>
+          <t>759371</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1453253</t>
+          <t>1467233</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1443197</t>
+          <t>1456489</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1461473</t>
+          <t>1474212</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624115</t>
+          <t>718509</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624115</t>
+          <t>718509</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624115</t>
+          <t>718509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846569</t>
+          <t>768638</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846569</t>
+          <t>768638</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846569</t>
+          <t>768638</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470683</t>
+          <t>1487147</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470683</t>
+          <t>1487147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470683</t>
+          <t>1487147</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>925001</t>
+          <t>794044</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>918947</t>
+          <t>788320</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>927996</t>
+          <t>796942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>712143</t>
+          <t>825200</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>707013</t>
+          <t>819478</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>715215</t>
+          <t>828288</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1637144</t>
+          <t>1619244</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1629592</t>
+          <t>1611966</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1642157</t>
+          <t>1623535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717096</t>
+          <t>830608</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717096</t>
+          <t>830608</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717096</t>
+          <t>830608</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645816</t>
+          <t>1628680</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645816</t>
+          <t>1628680</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645816</t>
+          <t>1628680</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65425</t>
+          <t>68745</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>103457</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3417184</t>
+          <t>3486850</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3398800</t>
+          <t>3470857</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3428620</t>
+          <t>3496648</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3658661</t>
+          <t>3680101</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3645006</t>
+          <t>3667311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3670348</t>
+          <t>3690909</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7075845</t>
+          <t>7166951</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7056554</t>
+          <t>7148967</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7092998</t>
+          <t>7183679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
